--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-cleaning-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-cleaning-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Outliers là những giá trị dị biệt, nằm cách xa phần lớn các điểm dữ liệu khác trong mẫu (ví dụ: tuổi nhân viên nhập là 200). Outliers có thể do sai sót nhập liệu hoặc là giá trị đặc biệt thực tế.</v>
       </c>
       <c r="F2" t="str">
+        <v>Các hàng dữ liệu bị trống hoàn toàn không chứa bất kỳ thông tin nào — dữ liệu khuyết thiếu null</v>
+      </c>
+      <c r="G2" t="str">
         <v>Các giá trị dữ liệu khác biệt quá lớn, lệch chuẩn hẳn so với phần lớn các quan trắc khác trong bộ dữ liệu — giá trị lệch chuẩn dị biệt</v>
       </c>
-      <c r="G2" t="str">
-        <v>Các hàng dữ liệu bị trống hoàn toàn không chứa bất kỳ thông tin nào — dữ liệu khuyết thiếu null</v>
-      </c>
       <c r="H2" t="str">
+        <v>Các câu lệnh SQL bị viết sai cú pháp khiến truy vấn không thể thực thi — lỗi cú pháp truy vấn</v>
+      </c>
+      <c r="I2" t="str">
         <v>Các trường dữ liệu chứa thông tin nhạy cảm của khách hàng cần được mã hóa bảo mật — dữ liệu nhạy cảm</v>
       </c>
-      <c r="I2" t="str">
-        <v>Các câu lệnh SQL bị viết sai cú pháp khiến truy vấn không thể thực thi — lỗi cú pháp truy vấn</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +492,7 @@
         <v>Đối với biến số liên tục như Tuổi, việc thay thế NULL bằng giá trị trung bình (mean) hoặc trung vị (median) là kỹ thuật điền khuyết (Imputation) cơ bản để giữ lại dòng dữ liệu phục vụ phân tích.</v>
       </c>
       <c r="F3" t="str">
-        <v>Điền giá trị mặc định là tuổi trung bình (mean) hoặc trung vị (median) của toàn bộ khách hàng có sẵn — điền giá trị đại diện</v>
+        <v>Bắt buộc người dùng phải gửi ảnh chụp căn cước công dân để hệ thống tự động trích xuất lại tuổi — yêu cầu xác thực cưỡng bức</v>
       </c>
       <c r="G3" t="str">
         <v>Xóa bỏ vĩnh viễn toàn bộ cơ sở dữ liệu của dự án và yêu cầu khách hàng đăng ký lại từ đầu — xóa database</v>
@@ -501,10 +501,10 @@
         <v>Tự động sinh ngẫu nhiên một con số từ 1 đến 100 để điền vào ô trống đó — sinh số ngẫu nhiên</v>
       </c>
       <c r="I3" t="str">
-        <v>Bắt buộc người dùng phải gửi ảnh chụp căn cước công dân để hệ thống tự động trích xuất lại tuổi — yêu cầu xác thực cưỡng bức</v>
+        <v>Điền giá trị mặc định là tuổi trung bình (mean) hoặc trung vị (median) của toàn bộ khách hàng có sẵn — điền giá trị đại diện</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>`isnull()` và `isna()` là hai hàm tương đương trong Pandas dùng để kiểm tra và phát hiện sự hiện diện của giá trị NULL/NaN trong dữ liệu.</v>
       </c>
       <c r="F4" t="str">
-        <v>isnull() hoặc isna() — trả về DataFrame dạng Boolean biểu thị ô nào bị khuyết — phát hiện giá trị khuyết</v>
+        <v>describe() — dùng để tính toán các thống kê mô tả cơ bản của DataFrame — thống kê mô tả</v>
       </c>
       <c r="G4" t="str">
         <v>dropna() — dùng để xóa bỏ trực tiếp các dòng chứa giá trị khuyết khỏi DataFrame — xóa dòng khuyết</v>
       </c>
       <c r="H4" t="str">
+        <v>isnull() hoặc isna() — trả về DataFrame dạng Boolean biểu thị ô nào bị khuyết — phát hiện giá trị khuyết</v>
+      </c>
+      <c r="I4" t="str">
         <v>fillna() — dùng để thay thế các giá trị khuyết bằng một giá trị chỉ định trước — điền giá trị khuyết</v>
       </c>
-      <c r="I4" t="str">
-        <v>describe() — dùng để tính toán các thống kê mô tả cơ bản của DataFrame — thống kê mô tả</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Trim/Strip giúp làm sạch chuỗi nhập liệu bị thừa khoảng trắng do người dùng gõ nhầm (ví dụ: " nguyen van a " -&gt; "nguyen van a"), giúp việc so sánh chuỗi chính xác.</v>
       </c>
       <c r="F5" t="str">
+        <v>Mã hóa chuỗi văn bản thành một chuỗi ký tự bảo mật không thể đọc được — mã hóa chuỗi</v>
+      </c>
+      <c r="G5" t="str">
         <v>Loại bỏ các khoảng trắng thừa ở đầu và cuối của chuỗi văn bản — loại bỏ khoảng trắng thừa</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Chuyển đổi toàn bộ chuỗi văn bản từ chữ thường sang chữ hoa in đậm — in hoa chuỗi</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Cắt chuỗi văn bản ra thành nhiều chuỗi con dựa trên ký tự ngăn cách — cắt chuỗi</v>
       </c>
-      <c r="I5" t="str">
-        <v>Mã hóa chuỗi văn bản thành một chuỗi ký tự bảo mật không thể đọc được — mã hóa chuỗi</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Trùng lặp dữ liệu khiến các phép tính SUM, COUNT bị cộng lặp, dẫn đến việc đưa ra các báo cáo phân tích sai lệch nghiêm trọng về quy mô thực tế.</v>
       </c>
       <c r="F6" t="str">
-        <v>Làm sai lệch kết quả thống kê tổng hợp (như thổi phồng số lượng khách hàng thực tế và tổng doanh thu) — sai lệch số liệu tổng</v>
+        <v>Làm hỏng ổ cứng vật lý lưu trữ cơ sở dữ liệu của máy chủ dự án — hỏng phần cứng</v>
       </c>
       <c r="G6" t="str">
-        <v>Làm hỏng ổ cứng vật lý lưu trữ cơ sở dữ liệu của máy chủ dự án — hỏng phần cứng</v>
+        <v>Làm cho giao diện hiển thị của dashboard bị chuyển sang chế độ ban đêm — thay đổi giao diện</v>
       </c>
       <c r="H6" t="str">
         <v>Tự động đổi mật khẩu đăng nhập của tất cả các khách hàng bị trùng lặp — lỗi đăng nhập</v>
       </c>
       <c r="I6" t="str">
-        <v>Làm cho giao diện hiển thị của dashboard bị chuyển sang chế độ ban đêm — thay đổi giao diện</v>
+        <v>Làm sai lệch kết quả thống kê tổng hợp (như thổi phồng số lượng khách hàng thực tế và tổng doanh thu) — sai lệch số liệu tổng</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Hàm `drop_duplicates()` loại bỏ nhanh các dòng trùng lặp hoàn toàn hoặc trùng lặp trên một tập hợp các cột chỉ định.</v>
       </c>
       <c r="F7" t="str">
-        <v>drop_duplicates() — loại bỏ các dòng bị trùng lặp và giữ lại dòng đầu tiên hoặc cuối cùng — xóa trùng lặp</v>
+        <v>dropna() — xóa bỏ các dòng chứa giá trị bị khuyết thiếu khỏi DataFrame — xóa dòng khuyết</v>
       </c>
       <c r="G7" t="str">
         <v>duplicated() — trả về mảng Boolean đánh dấu các dòng bị trùng lặp trong DataFrame — phát hiện trùng lặp</v>
       </c>
       <c r="H7" t="str">
-        <v>dropna() — xóa bỏ các dòng chứa giá trị bị khuyết thiếu khỏi DataFrame — xóa dòng khuyết</v>
+        <v>drop_duplicates() — loại bỏ các dòng bị trùng lặp và giữ lại dòng đầu tiên hoặc cuối cùng — xóa trùng lặp</v>
       </c>
       <c r="I7" t="str">
         <v>unique() — trả về danh sách các giá trị độc nhất trong một cột dữ liệu — lấy giá trị độc nhất</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Excel cung cấp tính năng "Remove Duplicates" giúp người dùng chọn các cột cần đối chiếu để tìm và xóa dòng trùng lặp chỉ qua vài click chuột.</v>
       </c>
       <c r="F8" t="str">
+        <v>Conditional Formatting (nằm trong tab Home) — công cụ tô màu đánh dấu dữ liệu trùng</v>
+      </c>
+      <c r="G8" t="str">
         <v>Remove Duplicates (nằm trong tab Data) — công cụ xóa trùng lặp tự động</v>
       </c>
-      <c r="G8" t="str">
-        <v>Conditional Formatting (nằm trong tab Home) — công cụ tô màu đánh dấu dữ liệu trùng</v>
-      </c>
       <c r="H8" t="str">
+        <v>Data Validation (nằm trong tab Data) — công cụ ràng buộc điều kiện nhập liệu</v>
+      </c>
+      <c r="I8" t="str">
         <v>Text to Columns (nằm trong tab Data) — công cụ chia tách chuỗi dữ liệu trong ô</v>
       </c>
-      <c r="I8" t="str">
-        <v>Data Validation (nằm trong tab Data) — công cụ ràng buộc điều kiện nhập liệu</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Không nhất quán định dạng là lỗi rất phổ biến khi thu thập dữ liệu từ nhiều nguồn hoặc do người dùng tự nhập tay không có ràng buộc (regex validation).</v>
       </c>
       <c r="F9" t="str">
+        <v>Số điện thoại của tất cả các khách hàng đều bắt đầu bằng chữ số 0 — quy định đầu số</v>
+      </c>
+      <c r="G9" t="str">
         <v>Một số dòng lưu dạng `0901234567`, số khác lưu dạng `+84901234567` hoặc `090-123-4567` — không nhất quán định dạng</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Số điện thoại của khách hàng có chứa đúng 10 chữ số tự nhiên — định dạng chuẩn</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Số điện thoại của tất cả các khách hàng đều bắt đầu bằng chữ số 0 — quy định đầu số</v>
       </c>
       <c r="I9" t="str">
         <v>Cột số điện thoại được lưu trữ dưới kiểu dữ liệu chuỗi văn bản (String) — kiểu dữ liệu chuẩn</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Khi import dữ liệu thô, nhiều cột số hoặc ngày tháng thường bị nhận diện nhầm thành kiểu chuỗi (String). Ép kiểu về đúng dạng (Numeric, Datetime) là bước bắt buộc để thực hiện các phép toán và truy vấn lọc thời gian.</v>
       </c>
       <c r="F10" t="str">
+        <v>Xóa bỏ toàn bộ dữ liệu đang lưu trong cột đó và đặt lại giá trị mặc định là 0 — xóa dữ liệu cột</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Tự động chia tách cột dữ liệu đó ra thành 3 cột độc lập khác nhau — phân tách cột</v>
+      </c>
+      <c r="H10" t="str">
         <v>Chuyển đổi kiểu dữ liệu của một cột về đúng định dạng mong muốn (ví dụ: chuyển cột ngày tháng đang dạng String về dạng Datetime) — đồng bộ kiểu dữ liệu</v>
       </c>
-      <c r="G10" t="str">
-        <v>Xóa bỏ toàn bộ dữ liệu đang lưu trong cột đó và đặt lại giá trị mặc định là 0 — xóa dữ liệu cột</v>
-      </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Mã hóa thông tin trong cột đó bằng một khóa mật khẩu bảo mật tuyệt đối — mã hóa cột</v>
       </c>
-      <c r="I10" t="str">
-        <v>Tự động chia tách cột dữ liệu đó ra thành 3 cột độc lập khác nhau — phân tách cột</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Hàm `fillna(value)` dùng để thay thế các giá trị NaN bằng một giá trị cố định. Trong trường hợp này, `.fillna(0)` sẽ điền số 0 vào tất cả các ô bị trống.</v>
       </c>
       <c r="F11" t="str">
-        <v>Thay thế toàn bộ các giá trị khuyết thiếu (NULL/NaN) trong DataFrame bằng con số 0 — điền giá trị 0 vào ô trống</v>
+        <v>Thay thế tất cả các giá trị số dương trong DataFrame bằng số 0 — đặt giá trị 0 cho số dương</v>
       </c>
       <c r="G11" t="str">
         <v>Xóa bỏ tất cả các dòng chứa giá trị khuyết thiếu khỏi DataFrame — xóa dòng khuyết</v>
       </c>
       <c r="H11" t="str">
-        <v>Thay thế tất cả các giá trị số dương trong DataFrame bằng số 0 — đặt giá trị 0 cho số dương</v>
+        <v>Thay thế toàn bộ các giá trị khuyết thiếu (NULL/NaN) trong DataFrame bằng con số 0 — điền giá trị 0 vào ô trống</v>
       </c>
       <c r="I11" t="str">
         <v>Tạo ra một DataFrame mới có cấu trúc giống hệt nhưng rỗng hoàn toàn — tạo DataFrame rỗng</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
